--- a/stories/arbres/ATOM-SOC.MET.001-05.xlsx
+++ b/stories/arbres/ATOM-SOC.MET.001-05.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -602,7 +602,6 @@
           <t>secondary_lessons</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -819,6 +818,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -833,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV6"/>
+  <dimension ref="A1:AW6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1127,6 +1138,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1151,7 +1167,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Héloïse marche avec papa. Ils voient la boulangerie. Le boulanger a un métier. Son geste utile, c'est le pain. Ils voient le cabinet. Le médecin a un métier. Son geste utile, c'est soigner. Ils voient l'école. La maîtresse a un métier. Son geste utile, c'est raconter. Un bus passe. Le chauffeur a un métier. Son geste utile, c'est conduire. Héloïse dit : métier. Papa dit : un geste utile. Maman les rejoint. Héloïse répète les métiers.</t>
+          <t>Héloïse marche avec papa. Ils voient la boulangerie. Le boulanger a un métier. Son geste utile, c'est le pain. Ils voient le cabinet. Le médecin a un métier. Son geste utile, c'est soigner. Ils voient l'école. La maîtresse a un métier. Son geste utile, c'est raconter. Un bus passe. Le chauffeur a un métier. Son geste utile, c'est conduire. Métier. Un geste utile. Maman les rejoint. Héloïse répète les métiers.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1289,6 +1305,14 @@
         <v>12</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Héloïse marche avec papa. Ils voient la boulangerie. Le boulanger a un métier. Son geste utile, c'est le pain. Ils voient le cabinet. Le médecin a un métier. Son geste utile, c'est soigner. Ils voient l'école. La maîtresse a un métier. Son geste utile, c'est raconter. Un bus passe. Le chauffeur a un métier. Son geste utile, c'est conduire.
+enfant-f|Métier.
+papa|Un geste utile. Maman les rejoint.
+narrateur|Héloïse répète les métiers.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1465,6 +1489,11 @@
       <c r="AV3" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|Le boulanger, le médecin, la maîtresse. Qu'est-ce que c'est ?</t>
         </is>
       </c>
     </row>
@@ -1633,6 +1662,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Héloïse a nommé les métiers. Chaque métier a un geste utile. Papa et maman étaient là.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1795,6 +1829,11 @@
         <v>12</v>
       </c>
       <c r="AV5" s="2" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Héloïse prend la main de maman. Ils rentrent.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1957,6 +1996,11 @@
         <v>12</v>
       </c>
       <c r="AV6" s="2" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -1975,7 +2019,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -1992,6 +2036,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-SOC.MET.001-05.xlsx
+++ b/stories/arbres/ATOM-SOC.MET.001-05.xlsx
@@ -844,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW6"/>
+  <dimension ref="A1:AX6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1143,6 +1143,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1313,6 +1318,7 @@
 narrateur|Héloïse répète les métiers.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1496,6 +1502,7 @@
           <t>narrateur|Le boulanger, le médecin, la maîtresse. Qu'est-ce que c'est ?</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1667,6 +1674,7 @@
           <t>narrateur|Héloïse a nommé les métiers. Chaque métier a un geste utile. Papa et maman étaient là.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1834,6 +1842,7 @@
           <t>narrateur|Héloïse prend la main de maman. Ils rentrent.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2001,6 +2010,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2019,7 +2029,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2043,6 +2053,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -2057,7 +2081,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2244,6 +2268,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/ATOM-SOC.MET.001-05.xlsx
+++ b/stories/arbres/ATOM-SOC.MET.001-05.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Héloïse nomme les métiers</t>
+          <t>Le camion rouge au loin</t>
         </is>
       </c>
     </row>
@@ -830,6 +830,18 @@
       <c r="B30" t="inlineStr">
         <is>
           <t>voix-roles-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>fil_rouge</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Nina veut voir le camion rouge. Sirène au loin. Papa et maman tiennent les mains, sur le trottoir. La caserne reste loin. Ils regardent, puis rentrent.</t>
         </is>
       </c>
     </row>
@@ -1172,12 +1184,12 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Héloïse marche avec papa. Ils voient la boulangerie. Le boulanger a un métier. Son geste utile, c'est le pain. Ils voient le cabinet. Le médecin a un métier. Son geste utile, c'est soigner. Ils voient l'école. La maîtresse a un métier. Son geste utile, c'est raconter. Un bus passe. Le chauffeur a un métier. Son geste utile, c'est conduire. Métier. Un geste utile. Maman les rejoint. Héloïse répète les métiers.</t>
+          <t>Au loin, une sirène chante très bas. Le son arrive au-dessus des toits. La rue du village est calme, encore. Nina vit ici, avec papa et maman. Le trottoir est chaud sous les sandales. J'entends le camion ! Oui, Nina. On reste ici. Sur le trottoir. Je veux voir le rouge. On regarde de loin. En ce moment, Nina prend deux mains. La main de papa, la main de maman. Un oiseau part d'un toit. La sirène reste loin, tout bas. Il est où ? Là-bas. Près de la caserne. Un point rouge avance, tout petit. Il brille entre deux maisons. Le camion ! Oui. C'est le pompier. C'est son métier. Pompier. Il aide. On le regarde d'ici. Nina se penche un peu. Ses sandales restent sur le trottoir. On reste ici, Nina. Pieds sur le trottoir. On tient les mains. Je tiens. La sirène descend, encore plus loin. Le point rouge passe, tout petit. Il va vite. Oui. Nous, on reste. Tu vois le camion ? Oui, papa. Un chien aboie derrière une porte. Puis il se tait. L'air sent la poussière chaude.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Héloïse marche avec papa. Ils voient la boulangerie. Le boulanger a un &lt;emphasis level="moderate"&gt;métier&lt;/emphasis&gt;. Son geste utile, c'est le pain. Ils voient le cabinet. Le médecin a un métier. Son geste utile, c'est soigner. Ils voient l'école. La maîtresse a un métier. Son geste utile, c'est raconter. Un bus passe. Le chauffeur a un métier. Son geste utile, c'est conduire. Héloïse dit : métier. Papa dit : un geste utile. Maman les rejoint. Héloïse répète les métiers.&lt;/prosody&gt;&lt;break time="400ms"/&gt;&lt;/speak&gt;</t>
+          <t>Au loin, une sirène chante très bas. Le son arrive au-dessus des toits. La rue du village est calme, encore. Nina vit ici, avec papa et maman. Le trottoir est chaud sous les sandales. J'entends le camion ! Oui, Nina. On reste ici. Sur le trottoir. Je veux voir le rouge. On regarde de loin. En ce moment, Nina prend deux mains. La main de papa, la main de maman. Un oiseau part d'un toit. La sirène reste loin, tout bas. Il est où ? Là-bas. Près de la caserne. Un point rouge avance, tout petit. Il brille entre deux maisons. Le camion ! Oui. C'est le pompier. C'est son métier. Pompier. Il aide. On le regarde d'ici. Nina se penche un peu. Ses sandales restent sur le trottoir. On reste ici, Nina. Pieds sur le trottoir. On tient les mains. Je tiens. La sirène descend, encore plus loin. Le point rouge passe, tout petit. Il va vite. Oui. Nous, on reste. Tu vois le camion ? Oui, papa. Un chien aboie derrière une porte. Puis il se tait. L'air sent la poussière chaude.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1233,14 +1245,14 @@
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
-          <t>slow</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="AA2" s="2" t="n">
         <v>0.86</v>
       </c>
       <c r="AB2" s="2" t="n">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
@@ -1312,13 +1324,51 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Héloïse marche avec papa. Ils voient la boulangerie. Le boulanger a un métier. Son geste utile, c'est le pain. Ils voient le cabinet. Le médecin a un métier. Son geste utile, c'est soigner. Ils voient l'école. La maîtresse a un métier. Son geste utile, c'est raconter. Un bus passe. Le chauffeur a un métier. Son geste utile, c'est conduire.
-enfant-f|Métier.
-papa|Un geste utile. Maman les rejoint.
-narrateur|Héloïse répète les métiers.</t>
-        </is>
-      </c>
-      <c r="AX2" t="inlineStr"/>
+          <t>narrateur|Au loin, une sirène chante très bas.
+narrateur|Le son arrive au-dessus des toits.
+narrateur|La rue du village est calme, encore.
+narrateur|Nina vit ici, avec papa et maman.
+narrateur|Le trottoir est chaud sous les sandales.
+enfant-f|J'entends le camion !
+papa|Oui, Nina.
+maman|On reste ici.
+maman|Sur le trottoir.
+enfant-f|Je veux voir le rouge.
+papa|On regarde de loin.
+narrateur|En ce moment, Nina prend deux mains.
+narrateur|La main de papa, la main de maman.
+narrateur|Un oiseau part d'un toit.
+narrateur|La sirène reste loin, tout bas.
+enfant-f|Il est où ?
+maman|Là-bas.
+maman|Près de la caserne.
+narrateur|Un point rouge avance, tout petit.
+narrateur|Il brille entre deux maisons.
+enfant-f|Le camion !
+papa|Oui.
+papa|C'est le pompier.
+papa|C'est son métier.
+enfant-f|Pompier.
+maman|Il aide.
+maman|On le regarde d'ici.
+narrateur|Nina se penche un peu.
+narrateur|Ses sandales restent sur le trottoir.
+papa|On reste ici, Nina.
+papa|Pieds sur le trottoir.
+maman|On tient les mains.
+enfant-f|Je tiens.
+narrateur|La sirène descend, encore plus loin.
+narrateur|Le point rouge passe, tout petit.
+enfant-f|Il va vite.
+maman|Oui.
+maman|Nous, on reste.
+papa|Tu vois le camion ?
+enfant-f|Oui, papa.
+narrateur|Un chien aboie derrière une porte.
+narrateur|Puis il se tait.
+narrateur|L'air sent la poussière chaude.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1343,12 +1393,12 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Le boulanger, le médecin, la maîtresse. Qu'est-ce que c'est ?</t>
+          <t>Le pompier a un camion. C'est quoi ?</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Le boulanger, le médecin, la maîtresse. Qu'est-ce que c'est ?&lt;/prosody&gt;&lt;break time="250ms"/&gt;&lt;/speak&gt;</t>
+          <t>Le pompier a un camion. C'est quoi ?</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -1363,7 +1413,7 @@
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>métier | un métier | geste utile | le pain</t>
+          <t>métier | un métier | son métier | le métier | c'est un métier</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
@@ -1378,7 +1428,7 @@
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>Chacun a un métier. Un geste utile. Que dit Héloïse ?</t>
+          <t>Il aide avec le camion. C'est quoi ?</t>
         </is>
       </c>
       <c r="M3" s="2" t="inlineStr"/>
@@ -1427,7 +1477,7 @@
         <v>0.8</v>
       </c>
       <c r="AB3" s="2" t="n">
-        <v>1.4</v>
+        <v>1.28</v>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
@@ -1499,10 +1549,10 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|Le boulanger, le médecin, la maîtresse. Qu'est-ce que c'est ?</t>
-        </is>
-      </c>
-      <c r="AX3" t="inlineStr"/>
+          <t>narrateur|Le pompier a un camion.
+narrateur|C'est quoi ?</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1527,12 +1577,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Héloïse a nommé les métiers. Chaque métier a un geste utile. Papa et maman étaient là.</t>
+          <t>Le point rouge devient tout petit. La sirène n'est plus qu'un fil. Il est parti. Oui. Le pompier fait son métier. Et nous, on est restés ici. Sur le trottoir. J'ai vu le rouge. Bravo, Nina. Tu as regardé de loin. Merci d'avoir tenu les mains. Nina serre encore les deux mains. Les sandales sont un peu poussiéreuses. On rentre ? Oui. On marche sur le trottoir. Un toit cache déjà la caserne. Il ne reste qu'un peu de silence.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Héloïse a nommé les &lt;emphasis level="moderate"&gt;métier&lt;/emphasis&gt;s. Chaque métier a un geste utile. Papa et maman étaient là.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Le point rouge devient tout petit. La sirène n'est plus qu'un fil. Il est parti. Oui. Le pompier fait son métier. Et nous, on est restés ici. Sur le trottoir. J'ai vu le rouge. Bravo, Nina. Tu as regardé de loin. Merci d'avoir tenu les mains. Nina serre encore les deux mains. Les sandales sont un peu poussiéreuses. On rentre ? Oui. On marche sur le trottoir. Un toit cache déjà la caserne. Il ne reste qu'un peu de silence.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1588,14 +1638,14 @@
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
-          <t>slow</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="AA4" s="2" t="n">
         <v>0.86</v>
       </c>
       <c r="AB4" s="2" t="n">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
@@ -1671,10 +1721,26 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Héloïse a nommé les métiers. Chaque métier a un geste utile. Papa et maman étaient là.</t>
-        </is>
-      </c>
-      <c r="AX4" t="inlineStr"/>
+          <t>narrateur|Le point rouge devient tout petit.
+narrateur|La sirène n'est plus qu'un fil.
+enfant-f|Il est parti.
+papa|Oui.
+papa|Le pompier fait son métier.
+maman|Et nous, on est restés ici.
+maman|Sur le trottoir.
+enfant-f|J'ai vu le rouge.
+papa|Bravo, Nina.
+papa|Tu as regardé de loin.
+maman|Merci d'avoir tenu les mains.
+narrateur|Nina serre encore les deux mains.
+narrateur|Les sandales sont un peu poussiéreuses.
+maman|On rentre ?
+enfant-f|Oui.
+papa|On marche sur le trottoir.
+narrateur|Un toit cache déjà la caserne.
+narrateur|Il ne reste qu'un peu de silence.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1699,12 +1765,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Héloïse prend la main de maman. Ils rentrent.</t>
+          <t>La maison sent le linge au soleil. Nina s'assoit sur le pas de la porte. Ses sandales tapent la pierre, tout doux. Le camion était rouge. Oui. Vu de loin. Le pompier aide, là-bas. Nous, on reste près de la maison. J'ai tenu les mains. Oui. Tu as bien fait. Tu veux de l'eau ? Oui, papa. L'eau est fraîche dans le verre. Nina boit, un peu trop vite. Doucement.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Héloïse prend la &lt;emphasis level="moderate"&gt;main&lt;/emphasis&gt; de maman. Ils rentrent.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>La maison sent le linge au soleil. Nina s'assoit sur le pas de la porte. Ses sandales tapent la pierre, tout doux. Le camion était rouge. Oui. Vu de loin. Le pompier aide, là-bas. Nous, on reste près de la maison. J'ai tenu les mains. Oui. Tu as bien fait. Tu veux de l'eau ? Oui, papa. L'eau est fraîche dans le verre. Nina boit, un peu trop vite. Doucement.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1760,14 +1826,14 @@
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
-          <t>slow</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="AA5" s="2" t="n">
         <v>0.86</v>
       </c>
       <c r="AB5" s="2" t="n">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
@@ -1839,10 +1905,24 @@
       <c r="AV5" s="2" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Héloïse prend la main de maman. Ils rentrent.</t>
-        </is>
-      </c>
-      <c r="AX5" t="inlineStr"/>
+          <t>narrateur|La maison sent le linge au soleil.
+narrateur|Nina s'assoit sur le pas de la porte.
+narrateur|Ses sandales tapent la pierre, tout doux.
+enfant-f|Le camion était rouge.
+maman|Oui.
+maman|Vu de loin.
+papa|Le pompier aide, là-bas.
+papa|Nous, on reste près de la maison.
+enfant-f|J'ai tenu les mains.
+maman|Oui.
+maman|Tu as bien fait.
+papa|Tu veux de l'eau ?
+enfant-f|Oui, papa.
+narrateur|L'eau est fraîche dans le verre.
+narrateur|Nina boit, un peu trop vite.
+maman|Doucement.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1867,12 +1947,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>La rue redevient calme. Plus de sirène, plus de point rouge. Je l'ai vu. Oui. De loin, sur le trottoir. Les sandales sèchent sur la pierre. Le toit garde le village, tout tranquille.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;L'histoire est finie.&lt;/prosody&gt;&lt;break time="600ms"/&gt;&lt;/speak&gt;</t>
+          <t>La rue redevient calme. Plus de sirène, plus de point rouge. Je l'ai vu. Oui. De loin, sur le trottoir. Les sandales sèchent sur la pierre. Le toit garde le village, tout tranquille.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -1928,14 +2008,14 @@
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
-          <t>slow</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="AA6" s="2" t="n">
         <v>0.82</v>
       </c>
       <c r="AB6" s="2" t="n">
-        <v>1.36</v>
+        <v>1.22</v>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
@@ -2007,10 +2087,15 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr"/>
+          <t>narrateur|La rue redevient calme.
+narrateur|Plus de sirène, plus de point rouge.
+enfant-f|Je l'ai vu.
+papa|Oui.
+maman|De loin, sur le trottoir.
+narrateur|Les sandales sèchent sur la pierre.
+narrateur|Le toit garde le village, tout tranquille.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2029,7 +2114,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2067,6 +2152,13 @@
       <c r="A5" t="inlineStr">
         <is>
           <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-SOC.MET.001-05.xlsx
+++ b/stories/arbres/ATOM-SOC.MET.001-05.xlsx
@@ -671,7 +671,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>quartier</t>
+          <t>trottoir du village, caserne vue de loin, pas de la porte</t>
         </is>
       </c>
     </row>
@@ -683,7 +683,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Héloïse, papa, maman</t>
+          <t>Nina, papa, maman</t>
         </is>
       </c>
     </row>
